--- a/data/wrinklesandfinelines.xlsx
+++ b/data/wrinklesandfinelines.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farha\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DE_Backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{380F94B2-C181-42B9-A281-0CFE91CD4AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0DDBDBA0-800F-475B-8711-827E03EC5E74}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -113,8 +112,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -504,17 +503,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2D3CBBC-CF51-4C73-A503-DC0835307BF2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="31.21875" customWidth="1"/>
-    <col min="2" max="2" width="23.33203125" customWidth="1"/>
-    <col min="3" max="3" width="28.33203125" customWidth="1"/>
-    <col min="4" max="4" width="64.88671875" customWidth="1"/>
+    <col min="1" max="1" width="31.19921875" customWidth="1"/>
+    <col min="2" max="2" width="23.296875" customWidth="1"/>
+    <col min="3" max="3" width="28.296875" customWidth="1"/>
+    <col min="4" max="4" width="64.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>20</v>
       </c>
@@ -528,7 +527,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -542,7 +541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -556,7 +555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -570,7 +569,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -584,7 +583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -598,7 +597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -612,7 +611,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -626,7 +625,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -640,7 +639,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -654,7 +653,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -668,7 +667,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -682,7 +681,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -696,7 +695,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -710,7 +709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -724,7 +723,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>0</v>
       </c>
